--- a/inquiry_forms/032_property_investment_interest_form--inquiry_forms.xlsx
+++ b/inquiry_forms/032_property_investment_interest_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'single-family_residence',_'label':_'single_family_residence'}</t>
+          <t>single_family_residence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'single-family_residence', 'label': 'single_family_residence'}</t>
+          <t>single family residence</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'condominium',_'label':_'condominium'}</t>
+          <t>condominium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'condominium', 'label': 'condominium'}</t>
+          <t>condominium</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'townhouse',_'label':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'townhouse', 'label': 'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'apartment',_'label':_'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'apartment', 'label': 'apartment'}</t>
+          <t>apartment</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'land',_'label':_'land'}</t>
+          <t>land</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'land', 'label': 'land'}</t>
+          <t>land</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'urban',_'label':_'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'urban', 'label': 'urban'}</t>
+          <t>urban</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'suburban',_'label':_'suburban'}</t>
+          <t>suburban</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'suburban', 'label': 'suburban'}</t>
+          <t>suburban</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'rural',_'label':_'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'rural', 'label': 'rural'}</t>
+          <t>rural</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'residential',_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'residential', 'label': 'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'commercial',_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'commercial', 'label': 'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'industrial',_'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'industrial', 'label': 'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'beginner', 'label': 'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'intermediate', 'label': 'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'advanced', 'label': 'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
     </row>
